--- a/www/download/IND.gross_output.s.du.rpO1.xlsx
+++ b/www/download/IND.gross_output.s.du.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634372.970973836</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>699783.865357608</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>708031.003611967</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>643013.415336067</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>685252.604319277</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>658162.268161235</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>616008.330882019</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>704703.032197188</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>886591.224382827</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.107</t>
+          <t>1107029.17181366</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1236915.59338804</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.329</t>
+          <t>1328732.61972933</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1598338.88759319</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>1768257.69046221</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1756569.10439711</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>510659.426153529</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>500036.635338645</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>454493.789429903</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>468905.121528184</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>462867.764255642</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>421284.028367891</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>427022.585354324</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>457421.386659118</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>560744.17530408</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>633449.522351477</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>654438.247042289</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>701606.176583241</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>803783.410866827</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>845001.342585954</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>795913.16514963</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>561484.387033053</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>548181.072289495</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>502982.854132865</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>519341.157206314</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>521833.164038024</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>486403.611172599</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>499067.716328148</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>526291.498334307</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>632862.397219383</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>725370.94704014</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>737170.861079544</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>793627.195869078</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>908468.050227477</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1013683.84926014</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>947633.3747133</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39095.9050432467</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41003.4374120515</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33163.1783934476</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36302.7431201266</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34868.0565243439</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32350.2250857051</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34238.5039092819</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37803.4315944699</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48685.0519566717</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60129.1352067366</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67403.029071526</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79716.1016114284</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104410.245817158</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127428.195104201</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124850.820357061</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>1087036.34956857</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1192957.98475986</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1225820.80847727</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>1204203.6511635</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>834311.617919726</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>989669.241823144</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>866496.779308652</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>804428.220042839</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>875427.061052626</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1072686.66761498</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1422173.11685508</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.703</t>
+          <t>1702727.90277668</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>2451091.98378094</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.015</t>
+          <t>3014779.59326862</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.974</t>
+          <t>2973757.44356738</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>999510.990237838</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>1044389.72284735</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1098613.16163829</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>1089129.98598098</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>1164169.30979227</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>1280922.55909655</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1272947.30480016</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1288324.13113855</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1490748.24759104</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1704931.75286724</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.918</t>
+          <t>1917830.40765721</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>2156912.61705416</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.339</t>
+          <t>2339416.60149698</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.514</t>
+          <t>2513709.33501509</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.292</t>
+          <t>2292222.10860094</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.902</t>
+          <t>2902445.01504557</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.469</t>
+          <t>3468668.92265845</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3.856</t>
+          <t>3855996.65874367</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4.065</t>
+          <t>4065303.65277976</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.229</t>
+          <t>4229478.83355574</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.614</t>
+          <t>4613735.28179539</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.016</t>
+          <t>5016046.17127506</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5.384</t>
+          <t>5383795.83068824</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6.248</t>
+          <t>6248127.59286126</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7.596</t>
+          <t>7596302.37036819</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>8.998</t>
+          <t>8997865.14331387</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.945</t>
+          <t>10945352.0135812</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>13.773</t>
+          <t>13772935.047858</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>17.682</t>
+          <t>17682216.9780851</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18919875.089004</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13341.4789525891</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13855.4286762487</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13488.6769903916</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13967.8097853572</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14139.9825717788</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13191.5896537208</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13353.2138846032</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15092.0785409474</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19498.641928414</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22651.1076583971</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24196.8231484183</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26021.100349962</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29873.1612337792</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35746.5819477757</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34033.1560755415</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132496.595890047</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178563.578968708</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172987.908103661</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188417.930879679</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179785.673235988</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>170238.191939463</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192899.883806011</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232610.779922405</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>279951.391161646</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>326674.302596365</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>363435.875476606</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>424061.491097692</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>506235.43918018</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>562728.685415349</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>447316.50522589</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.948</t>
+          <t>4947990.78960918</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.774</t>
+          <t>4773970.58300242</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.266</t>
+          <t>4265746.49761753</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4.366</t>
+          <t>4366492.3181592</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.277</t>
+          <t>4276618.77351698</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.003</t>
+          <t>4002735.61084127</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.982</t>
+          <t>3982415.76739053</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.185</t>
+          <t>4184757.32500611</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4989834.1909519</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.579</t>
+          <t>5578568.70274526</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5.632</t>
+          <t>5631552.66789105</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>5.896</t>
+          <t>5896206.47098969</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>6.655</t>
+          <t>6655382.51572019</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6.835</t>
+          <t>6834821.26286791</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>6.229</t>
+          <t>6229475.65727599</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>318934.04158826</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>323970.347311464</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>299413.138284963</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>314615.745288633</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>312324.693002696</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>289355.556782339</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>294768.897609232</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>318180.595881543</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>386590.700770269</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>437603.232808565</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>461464.414402635</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>491036.31226198</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>564649.642256211</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>598743.762097859</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>563792.419133866</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1205365.28586172</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1259942.4443386</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>1184965.67153244</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1251072.25326645</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1285855.65959269</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.234</t>
+          <t>1233993.03998354</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.302</t>
+          <t>1301883.84393454</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1484329.77190524</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1892030.18758428</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.217</t>
+          <t>2216588.57367474</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2.426</t>
+          <t>2426325.26461388</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2.662</t>
+          <t>2661503.18941809</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>3.076</t>
+          <t>3075894.90826699</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3.217</t>
+          <t>3217024.54599308</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.849</t>
+          <t>2848662.75417122</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10235.6727979456</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11544.8923535928</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12261.4561919576</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13579.6338204981</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12589.6721239373</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13493.7126401131</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14802.2043378989</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16550.841607722</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21297.6951259755</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27175.1683322543</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30713.5040264709</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35036.8075196663</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44055.4442314611</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51564.3217576879</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40160.8966815178</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>306024.786060198</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>300652.380588713</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>286995.239315165</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>299485.713067776</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>301632.640021365</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>286043.772806934</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>291014.527826246</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>310593.481526674</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>377157.218447889</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>435237.185736005</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>459498.168315724</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>494868.666090532</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>568472.465273957</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>604483.318460907</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>544505.68885294</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.576</t>
+          <t>2576210.54916012</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.591</t>
+          <t>2591093.33732387</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.358</t>
+          <t>2357533.33760878</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2419628.92931087</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.464</t>
+          <t>2464098.90802912</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.305</t>
+          <t>2304836.11507252</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.336</t>
+          <t>2335946.03224799</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.526</t>
+          <t>2526404.14479532</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3.063</t>
+          <t>3062760.01368446</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3.503</t>
+          <t>3503478.1956295</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3.664</t>
+          <t>3663683.6504919</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3.842</t>
+          <t>3841945.61810293</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>4378021.53379428</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>4.568</t>
+          <t>4568309.38538071</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>4.317</t>
+          <t>4317218.3514631</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.178</t>
+          <t>2178417.55997443</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.248</t>
+          <t>2247895.08473401</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>2468434.00415673</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>2638357.77877417</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.693</t>
+          <t>2692628.63670575</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.663</t>
+          <t>2662974.81989724</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.643</t>
+          <t>2643403.21506474</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.865</t>
+          <t>2864794.34895275</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3.256</t>
+          <t>3255648.42998579</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3860141.92122834</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>4.156</t>
+          <t>4155799.54074163</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4.395</t>
+          <t>4394729.45293634</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>5.009</t>
+          <t>5009050.63975796</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>4.553</t>
+          <t>4552568.62771302</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3919755.86344081</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>189564.341130488</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>202645.045437574</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>195552.480887494</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>196434.68075379</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204556.389041348</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191032.828839564</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>192095.99254634</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232841.41237196</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>298904.353635077</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>343872.825229773</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>364465.305637319</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>400882.833504104</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>459807.81732728</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>511396.321591536</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>480117.208346134</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124923.380918441</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>124152.040610457</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127280.384590126</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>130881.795896725</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>133539.096807122</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135731.479216264</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144464.190735084</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168815.498058795</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>206537.013520092</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>245454.135111542</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>266135.815712359</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>271835.459488522</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319532.412795949</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>322041.323674551</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250923.703524406</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>483344.611421477</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>586580.922244131</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>617980.720681076</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>247254.58107223</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377818.305794295</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>402202.796060631</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>373945.192748195</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>446081.110328502</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>512430.316445369</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>534029.931668243</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>544186.816808399</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>725914.864424581</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>850018.680429933</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.059</t>
+          <t>1059342.38849871</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1133087.1320757</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>946805.438671238</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>932209.578156858</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>1066700.01934219</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>1038969.68504953</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>1077187.67469671</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>1155756.15957009</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1202225.18650366</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1251249.5167042</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1449298.58403458</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>1698854.27522354</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>1991032.09807453</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2.299</t>
+          <t>2299044.1599376</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2.887</t>
+          <t>2886634.87460927</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3.116</t>
+          <t>3115535.31729514</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>3.201</t>
+          <t>3200711.10547914</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158626.80139862</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169225.359914136</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178564.284019512</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>185889.859628366</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200503.741122844</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204699.615249624</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>220826.232977785</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234671.089941281</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299595.649878173</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>358753.112971277</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>398028.534588924</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>444072.863728808</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>529025.078362379</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>552328.565006025</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>494077.040048847</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.358</t>
+          <t>2358394.41355455</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.605</t>
+          <t>2605067.436525</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.539</t>
+          <t>2539380.4094082</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.538</t>
+          <t>2537603.76006007</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.508</t>
+          <t>2508397.92197909</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.307</t>
+          <t>2306551.87905768</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.344</t>
+          <t>2343593.72996832</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.568</t>
+          <t>2567638.68052705</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>3173340.71985881</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3.603</t>
+          <t>3603314.2251083</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3.761</t>
+          <t>3761464.58967139</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3.999</t>
+          <t>3998981.92145261</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>4.546</t>
+          <t>4545673.82216311</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>4.562</t>
+          <t>4561758.43229972</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>4.021</t>
+          <t>4021096.31639125</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10.257</t>
+          <t>10257194.8356599</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.981</t>
+          <t>8981132.05909235</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8.387</t>
+          <t>8387470.34166975</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.659</t>
+          <t>7659418.51185327</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.776</t>
+          <t>8776226.08909496</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9.457</t>
+          <t>9456512.50452406</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8350221.1746056</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7.876</t>
+          <t>7876480.07578225</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8.437</t>
+          <t>8436664.73548321</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9239724.65348118</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9.224</t>
+          <t>9223557.53518076</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8.999</t>
+          <t>8999130.44886473</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9210308.29630185</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10.571</t>
+          <t>10571343.5166978</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10.225</t>
+          <t>10225338.3380732</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>1706835.25625428</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.894</t>
+          <t>1893836.58051246</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.765</t>
+          <t>1765439.26272485</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.218</t>
+          <t>1217747.31843259</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1471105.22034596</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1724357.48887875</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>1663075.63366519</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1861853.07513373</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.114</t>
+          <t>2113946.97616843</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>2435281.00056449</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2980216.78017985</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3.364</t>
+          <t>3363548.40254289</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3700107.12949776</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3.618</t>
+          <t>3617655.26627425</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3.208</t>
+          <t>3208213.19113769</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14464.446514201</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19071.7242114505</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22189.5537666091</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24522.803840913</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23247.974001583</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23315.9862684291</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25523.8107840865</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28554.3713076982</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37298.5973268051</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46808.9338808775</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54904.1697197918</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63575.9930035974</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80245.233016084</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>100329.889914904</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77105.0103437563</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28105.3258420298</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27350.2580872363</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25464.7976317536</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26845.3953995845</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26745.3015188767</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25497.5603942911</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26941.7952178576</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29889.4511358578</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38445.570045676</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45906.2358757709</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48254.8623107309</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50836.6446026714</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58892.8346447225</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69415.7152865741</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66533.7167159731</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10373.7720505159</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11876.8301017459</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14031.0222868052</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14805.5501350679</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14318.1941880731</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14246.7233918414</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15037.6112106513</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16572.619379234</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20960.1979860677</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25751.6369477021</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32387.547558424</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41999.5533667834</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60165.0607456471</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72547.5741443617</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47948.9062240063</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>447734.565437532</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>505938.628529752</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>620662.574174235</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>717035.518443683</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>831974.271047713</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1014039.43695564</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>1109109.37391237</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1117543.18854309</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1060533.66301364</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1104274.58928951</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.231</t>
+          <t>1231123.37753673</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1325960.43601099</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1397764.02282903</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1473572.01650205</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1190549.34720253</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7629.55160046804</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7652.02719661031</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7262.23696659852</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8103.95200641658</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8530.79712289475</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8964.26511972902</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8042.42383722026</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8848.50239240012</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10391.4379700989</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11329.2618545472</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11492.2244505966</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12480.7948523151</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13971.8519711275</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17193.1120088509</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14807.8475778236</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>747053.451819222</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>743279.811296978</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>685104.153219837</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>710003.487665174</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>719260.588712763</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>682748.109295269</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>699529.232453708</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>765641.61008817</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.933</t>
+          <t>932700.78676433</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>1065634.02828634</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>1097506.94789856</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1161988.60786549</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1337561.79118063</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1477878.14736793</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1363346.36200214</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>622370.164969478</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>681686.049756424</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>683544.892531379</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>782319.669949754</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>772178.121150828</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>604775.073111376</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>597757.966730636</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>566716.615706512</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>602638.192425798</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>682367.131294563</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.803</t>
+          <t>802686.23663643</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>859230.120373511</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1065420.17097542</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>1259131.73186053</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>983402.793916917</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236030.274603288</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251676.602704513</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246200.548752343</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259335.393092989</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264672.621717817</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>258344.249673105</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>267073.474268084</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>290166.386904144</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>348926.344728717</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>399368.007892955</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>416552.592534352</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>432542.041762873</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>495471.309399575</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>545692.054806942</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>473723.136509348</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136556.656376125</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147190.271356225</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123443.452775634</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>160134.016570794</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122626.044251316</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136574.122103175</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171582.420706207</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194947.739792596</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249195.768177572</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>240391.303494516</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>354143.984768849</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>431288.554588102</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>553004.090530035</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>694894.840280088</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>532233.539871751</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>715479.620479187</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>892171.86247308</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>900605.652315374</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>701835.776598856</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>405469.915920464</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>528770.340954296</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630870.180416996</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>746473.959501352</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>908735.051289537</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1173804.92679191</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1482320.45522483</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.852</t>
+          <t>1852032.4892235</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2410442.40610104</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3.011</t>
+          <t>3010544.47773749</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>2256226.38378846</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40965.2205264792</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47089.4530454274</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48600.2051358943</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52270.1281261434</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45750.0268185067</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46171.6237583108</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50137.2613583073</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57284.0131612317</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79519.0307152261</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92049.3539379987</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102543.948225066</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121148.753990753</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156475.818475363</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>197276.085867573</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>175270.121870659</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65874.6900227172</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64035.9872677196</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60636.9505538962</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63484.7729215065</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62105.0745837921</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58073.4998597681</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59395.077585181</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64868.7798367998</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79764.0299222053</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93217.6189851008</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98989.9793495888</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105724.151938372</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126497.922202642</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>146955.876286152</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129678.350489908</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>477638.823639955</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>533345.238454462</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>497501.495941634</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>506462.219707482</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>506919.068092304</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>501645.214145521</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>476546.390687192</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>520704.166493948</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>639790.351953341</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>725594.965163918</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>747258.623728116</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>781491.046797919</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>915625.538267309</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>916003.518434327</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>765468.384948103</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>363629.641062554</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>419927.346487464</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>475017.479933016</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>524680.734731301</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>547088.197591122</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>590015.973042383</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>438573.595073123</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492057.086925439</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>627641.46026221</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>798879.150464548</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.015</t>
+          <t>1014506.63617945</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1078760.49548201</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>1282140.40636932</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1398301.50551674</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1158070.49517619</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>622755.873474354</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>621102.934866926</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>628728.778415356</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>566342.76212683</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>615082.350081238</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>684294.209457754</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>601643.383665092</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>601016.269592191</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>638488.977292587</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>744637.008261008</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>812921.126530545</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>878954.389470009</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>936425.358027907</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1022004.0655568</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>823764.396953936</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10.509</t>
+          <t>10509232.4844567</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10.882</t>
+          <t>10882157.7426732</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>11.647</t>
+          <t>11646981.736692</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12.515</t>
+          <t>12514586.9632258</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>13.289</t>
+          <t>13288825.0280754</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>14.191</t>
+          <t>14191140.984164</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>14.363</t>
+          <t>14363325.4678359</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>14.446</t>
+          <t>14446128.0752296</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>14.952</t>
+          <t>14951681.4768317</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>15.755</t>
+          <t>15754964.010187</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16.744</t>
+          <t>16743769.9705473</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>17840370.8480075</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>18.715</t>
+          <t>18715285.029118</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>19.594</t>
+          <t>19593625.4138791</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>17.727</t>
+          <t>17727238.0142522</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5.487</t>
+          <t>5487103.09086572</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6.009</t>
+          <t>6009477.54139481</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6.093</t>
+          <t>6093279.48065094</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5.682</t>
+          <t>5681901.25606844</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5829811.83114936</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6.413</t>
+          <t>6412510.15369054</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6.369</t>
+          <t>6368874.19585171</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6.521</t>
+          <t>6520654.39186475</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>7.464</t>
+          <t>7463908.36111671</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8.851</t>
+          <t>8851443.99394753</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10.695</t>
+          <t>10694717.4121162</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>12.413</t>
+          <t>12413235.6924967</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>14.481</t>
+          <t>14480929.9608889</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>18.492</t>
+          <t>18491647.1669537</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>16.603</t>
+          <t>16603432.0870598</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060688.4328249</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>122789481.799157</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
